--- a/jogos_2025-05-20.xlsx
+++ b/jogos_2025-05-20.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Naftan</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['2', '22', '32']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45797.5</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Naftan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.25</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
         <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['2', '23', '32']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.5</v>
+        <v>1.06</v>
       </c>
       <c r="AI5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45797.5</v>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Urooba</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.35</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>8.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>3.95</v>
+        <v>6.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['4', '48']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['50', '75', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.6</v>
+        <v>1.14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45797.58333333334</v>
@@ -1923,35 +1923,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dibba Al Hisn</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>6.8</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.5</v>
+        <v>4.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X12" t="n">
         <v>4</v>
       </c>
-      <c r="T12" t="n">
+      <c r="Y12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['20', '39', '55', '71']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['5', '52', '71']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['32', '65']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>5</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>2.53</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45797.58333333334</v>
@@ -2052,29 +2052,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Al Urooba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>3.35</v>
       </c>
       <c r="M13" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>1.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.1</v>
+        <v>2.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>6.15</v>
+        <v>3.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['4', '48']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '75', '84']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.14</v>
+        <v>2.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45797.58333333334</v>
@@ -2181,35 +2181,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Dibba Al Hisn</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.61</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.47</v>
+        <v>3.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.22</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['5', '52', '71']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '65']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45797.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,65 +2346,65 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="T15" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.5</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>2.61</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.69</v>
+        <v>5.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['20', '39', '55', '71']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45797.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.62</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['43', '57']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.12</v>
       </c>
-      <c r="X19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['45+3', '67']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['1', '34', '58']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45797.625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>2.23</v>
       </c>
       <c r="M20" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>2.63</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['43', '57']</t>
+          <t>['45+3', '67']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['1', '34', '58']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45797.625</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['27', '32', '50', '86']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['24', '62']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.62</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['14', '38', '89']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45797.66666666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['27', '32', '50', '86']</t>
+          <t>['14', '38', '89']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['24', '62']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45797.66666666666</v>
